--- a/preview/pr-25/CodeSystem-pcor-questionnaire-catalogue.xlsx
+++ b/preview/pr-25/CodeSystem-pcor-questionnaire-catalogue.xlsx
@@ -180,7 +180,7 @@
     <t>GSLTPAQ</t>
   </si>
   <si>
-    <t>Godin-Shephard Leisure-Time Physical Activity Questionnaire, PCOR-MII-Eigenübersetzung</t>
+    <t>Godin-Shephard Leisure-Time Physical Activity Questionnaire, deutsche Übersetzung aus SOMACROSS 2.0 (UKE)</t>
   </si>
   <si>
     <t>expect</t>
